--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>3.02</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>8.550000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M10" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>8.550000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>3.32</v>
       </c>
       <c r="M12" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="N12" t="n">
-        <v>8.550000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,482 +2394,6 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46072.875</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ASO Chlef</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CS Constantine</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3" t="n">
-        <v>46072.875</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>MB Rouisset</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="3" t="n">
-        <v>46072.875</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MC Oran</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="3" t="n">
-        <v>46072.875</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Spanish Town Police FC</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="3" t="n">
         <v>46072.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.32</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.78</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>8.550000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>3.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="N10" t="n">
-        <v>8.550000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.32</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.78</v>
+        <v>4.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.32</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.78</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>8.550000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>3.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="N10" t="n">
-        <v>8.550000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>8.550000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>8.550000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M10" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>8.550000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -698,34 +698,34 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -698,34 +698,34 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46072.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>3.66</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.9</v>
+        <v>3.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>5.15</v>
+        <v>2.91</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.95</v>
+        <v>3.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>3.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.54</v>
+        <v>12.9</v>
       </c>
       <c r="R8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.33</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="AB8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.05</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>7.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>3.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="N10" t="n">
-        <v>8.550000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1858,64 +1858,64 @@
         <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
         <v>3.85</v>
       </c>
       <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1385,7 +1385,7 @@
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.66</v>
+        <v>3.28</v>
       </c>
       <c r="Q8" t="n">
         <v>12.9</v>
@@ -1406,7 +1406,7 @@
         <v>3.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
@@ -1424,16 +1424,16 @@
         <v>3.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG8" t="n">
         <v>1.05</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="M10" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>8.550000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
-        <v>1.85</v>
+        <v>4.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.75</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.93</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.94</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>8.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.31</v>
+        <v>2.93</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>2.94</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.93</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>7.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>3.28</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.9</v>
+        <v>3.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>5.15</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>2.59</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.95</v>
+        <v>3.72</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>7.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>8.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>2.93</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>2.94</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.32</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH12" t="n">
-        <v>2.94</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46072.79166666666</v>
+        <v>46072.8125</v>
       </c>
     </row>
     <row r="14">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2156,245 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46072.8125</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Austria 2. Liga</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Austria Klagenfurt</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SV Stripfing Weiden</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3" t="n">
         <v>46072.875</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Spanish Town Police FC</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="3" t="n">
-        <v>46072.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>2.52</v>
       </c>
       <c r="P7" t="n">
-        <v>3.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.9</v>
+        <v>3.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>5.15</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>3.48</v>
+        <v>6.25</v>
       </c>
       <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.22</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AH7" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.93</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>7.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.32</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="N10" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.94</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.25</v>
+        <v>1.85</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>8.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.32</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V11" t="n">
-        <v>11</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -778,70 +778,70 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.55</v>
+        <v>3.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="P3" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>6.4</v>
+        <v>6.85</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
         <v>1.2</v>
@@ -921,10 +921,10 @@
         <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>6.7</v>
@@ -957,7 +957,7 @@
         <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AG4" t="n">
         <v>1.78</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.93</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>7.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1376,7 +1376,7 @@
         <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="N8" t="n">
         <v>2.92</v>
@@ -1385,7 +1385,7 @@
         <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
         <v>3.54</v>
@@ -1409,7 +1409,7 @@
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
         <v>1.17</v>
@@ -1421,10 +1421,10 @@
         <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
         <v>1.33</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>2.52</v>
       </c>
       <c r="P9" t="n">
-        <v>3.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.9</v>
+        <v>4.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>5.15</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>3.48</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.22</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AH9" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>1.85</v>
+        <v>4.49</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.75</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.93</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.94</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.32</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
-        <v>4.49</v>
+        <v>1.85</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>8.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.93</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>2.52</v>
       </c>
       <c r="P7" t="n">
-        <v>3.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.9</v>
+        <v>4.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>3.48</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.22</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AH7" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2.25</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="AF8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.05</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>7.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.44</v>
+        <v>3.26</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.12</v>
+        <v>3.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="O10" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.5</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.49</v>
+        <v>1.85</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>8.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.93</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>2.99</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="N12" t="n">
-        <v>9.5</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.75</v>
+        <v>3.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.93</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.05</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.14</v>
+        <v>4.35</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.94</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O3" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>1.36</v>
@@ -820,7 +820,7 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
         <v>1.89</v>
@@ -829,7 +829,7 @@
         <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="AD3" t="n">
         <v>1.27</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="O4" t="n">
         <v>4.2</v>
@@ -924,7 +924,7 @@
         <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
         <v>6.7</v>
@@ -936,19 +936,19 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
         <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="AD4" t="n">
         <v>1.28</v>
@@ -960,7 +960,7 @@
         <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
         <v>1.24</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.93</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="AE7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.05</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>7.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>3.28</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.9</v>
+        <v>3.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>2.59</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.95</v>
+        <v>3.72</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>7.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>4.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="N10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.31</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>3.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>1.85</v>
+        <v>4.49</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.75</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.93</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.94</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.99</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.22</v>
+        <v>8.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.31</v>
+        <v>2.93</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.27</v>
       </c>
-      <c r="V12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>2.94</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M8" t="n">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.54</v>
+        <v>4.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.44</v>
+        <v>3.26</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.12</v>
+        <v>3.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.99</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>8.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>2.93</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.27</v>
       </c>
-      <c r="V10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>2.94</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>2.99</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="N12" t="n">
-        <v>9.5</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.75</v>
+        <v>3.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.93</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.05</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.14</v>
+        <v>4.35</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.94</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O13" t="n">
         <v>3.1</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46072.8125</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -781,25 +781,25 @@
         <v>3.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>3.68</v>
+        <v>4.58</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
         <v>2.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
         <v>2.89</v>
@@ -820,10 +820,10 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
         <v>1.81</v>
@@ -832,7 +832,7 @@
         <v>2.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
         <v>1.75</v>
@@ -841,10 +841,10 @@
         <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
         <v>2.06</v>
@@ -921,10 +921,10 @@
         <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>6.7</v>
@@ -936,16 +936,16 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
         <v>3.34</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.86</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
         <v>2.65</v>
@@ -1263,28 +1263,28 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="R7" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>5.15</v>
       </c>
       <c r="T7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.88</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.87</v>
-      </c>
       <c r="V7" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.22</v>
@@ -1293,7 +1293,7 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
         <v>6.95</v>
@@ -1305,16 +1305,16 @@
         <v>3.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AD7" t="n">
         <v>1.93</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
         <v>1.05</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="O8" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.12</v>
+        <v>3.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.65</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.91</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>3.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
         <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
         <v>3.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>4.49</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="M12" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>23</v>
+        <v>3.75</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>1.05</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.6</v>
+        <v>23</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>1.05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -900,25 +900,25 @@
         <v>3.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
       <c r="T4" t="n">
         <v>2.82</v>
@@ -948,7 +948,7 @@
         <v>1.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AD4" t="n">
         <v>1.28</v>
@@ -960,10 +960,10 @@
         <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46072.58333333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>3.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>5.15</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.95</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.81</v>
+        <v>3.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.93</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AE9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.05</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>7.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="M11" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.5</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.36</v>
       </c>
-      <c r="AA12" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.75</v>
+        <v>23</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>23</v>
+        <v>3.75</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.05</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>3.24</v>
       </c>
       <c r="M10" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>4.38</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>6.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.14</v>
+        <v>2.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>5.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.05</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.24</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.38</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>9.199999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.36</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.3</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.05</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.05</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.99</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>2.84</v>
+        <v>4.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>8.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AB12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>3.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
         <v>3.1</v>
@@ -1986,13 +1986,13 @@
         <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
         <v>1.28</v>
@@ -2004,19 +2004,19 @@
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
         <v>2.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
         <v>4.33</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="M3" t="n">
         <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
         <v>2.51</v>
@@ -799,13 +799,13 @@
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
         <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
         <v>6.85</v>
@@ -820,31 +820,31 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
         <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
         <v>1.95</v>
@@ -912,22 +912,22 @@
         <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
@@ -936,19 +936,19 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
         <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
         <v>1.28</v>
@@ -963,7 +963,7 @@
         <v>1.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46072.58333333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1263,10 +1263,10 @@
         <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
         <v>4</v>
@@ -1275,7 +1275,7 @@
         <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
         <v>2.88</v>
@@ -1287,16 +1287,16 @@
         <v>6.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
         <v>1.98</v>
@@ -1308,7 +1308,7 @@
         <v>3.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
         <v>1.76</v>
@@ -1317,10 +1317,10 @@
         <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="N8" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
         <v>2.85</v>
@@ -1388,19 +1388,19 @@
         <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.66</v>
+        <v>3.19</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="T8" t="n">
         <v>2.59</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
         <v>6.5</v>
@@ -1427,10 +1427,10 @@
         <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>2.18</v>
@@ -1507,7 +1507,7 @@
         <v>3.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.1</v>
@@ -1525,34 +1525,34 @@
         <v>3.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
         <v>1.05</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="M10" t="n">
         <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
         <v>4.38</v>
@@ -1629,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
         <v>2.17</v>
@@ -1647,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
         <v>1.53</v>
@@ -1656,22 +1656,22 @@
         <v>2.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AD10" t="n">
         <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
         <v>1.35</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.99</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>8.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.36</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>3.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>2.87</v>
       </c>
       <c r="M12" t="n">
-        <v>4.75</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.05</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.05</v>
+        <v>1.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N3" t="n">
         <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>4.58</v>
       </c>
       <c r="P3" t="n">
         <v>2.08</v>
@@ -799,13 +799,13 @@
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="T3" t="n">
         <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
         <v>6.85</v>
@@ -826,7 +826,7 @@
         <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.14</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
@@ -945,7 +945,7 @@
         <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
         <v>3.05</v>
@@ -957,7 +957,7 @@
         <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
         <v>1.78</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.47</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>3.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>12.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="S7" t="n">
-        <v>2.92</v>
+        <v>5.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98</v>
+        <v>1.26</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.33</v>
+        <v>1.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>7.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>2.47</v>
       </c>
       <c r="P9" t="n">
-        <v>3.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.6</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>5.15</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.26</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.79</v>
+        <v>3.33</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.94</v>
       </c>
-      <c r="AE9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>8.75</v>
       </c>
       <c r="O10" t="n">
-        <v>4.38</v>
+        <v>1.82</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>9.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>9.199999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.36</v>
+        <v>3.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>8.75</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
-        <v>1.82</v>
+        <v>4.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.57</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>2.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.05</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>23</v>
+        <v>3.5</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.87</v>
+        <v>24</v>
       </c>
       <c r="M3" t="n">
-        <v>3.44</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>1.06</v>
       </c>
       <c r="O3" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -903,7 +903,7 @@
         <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -912,7 +912,7 @@
         <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -921,13 +921,13 @@
         <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
         <v>3.34</v>
@@ -945,7 +945,7 @@
         <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>3.05</v>
@@ -957,10 +957,10 @@
         <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
         <v>1.24</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>2.47</v>
       </c>
       <c r="P7" t="n">
-        <v>3.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.6</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>5.15</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.26</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.79</v>
+        <v>3.33</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.94</v>
       </c>
-      <c r="AE7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.47</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>3.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>12.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="S9" t="n">
-        <v>2.92</v>
+        <v>5.15</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>1.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.33</v>
+        <v>1.79</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>7.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>2.87</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>2.87</v>
       </c>
       <c r="N10" t="n">
-        <v>8.75</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.82</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.57</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>6.55</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.37</v>
+        <v>8.75</v>
       </c>
       <c r="O11" t="n">
-        <v>4.38</v>
+        <v>1.82</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>9.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>9.199999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.36</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O12" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.5</v>
+        <v>24</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.96</v>
+        <v>1.06</v>
       </c>
       <c r="O2" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -900,16 +900,16 @@
         <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
         <v>2.6</v>
@@ -921,10 +921,10 @@
         <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
         <v>6.65</v>
@@ -945,7 +945,7 @@
         <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
         <v>3.05</v>
@@ -957,7 +957,7 @@
         <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AG4" t="n">
         <v>1.24</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.33</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M8" t="n">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="P8" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.76</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.87</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>2.87</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>11.15</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="P10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="AB10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.51</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.31</v>
+        <v>3.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>2.87</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="N11" t="n">
-        <v>8.75</v>
+        <v>2.43</v>
       </c>
       <c r="O11" t="n">
-        <v>1.82</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.57</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.38</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
         <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
         <v>4.38</v>
@@ -1864,7 +1864,7 @@
         <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R12" t="n">
         <v>1.61</v>
@@ -1891,7 +1891,7 @@
         <v>1.53</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AA12" t="n">
         <v>2.62</v>
@@ -1906,10 +1906,10 @@
         <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
         <v>1.35</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="M13" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>3.1</v>
@@ -1995,7 +1995,7 @@
         <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
         <v>8.1</v>
@@ -2004,25 +2004,25 @@
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
         <v>4.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
         <v>1.91</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>1.06</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.8</v>
+        <v>24</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>1.06</v>
       </c>
       <c r="O3" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>1.13</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>19</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.09</v>
+        <v>3.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.19</v>
+        <v>12.21</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="S7" t="n">
-        <v>3.17</v>
+        <v>4.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.59</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="W7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.05</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z7" t="n">
-        <v>3.72</v>
+        <v>6.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>3.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.18</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>6.15</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1385,25 +1385,25 @@
         <v>2.47</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
@@ -1412,22 +1412,22 @@
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
         <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
         <v>1.76</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>2.86</v>
       </c>
       <c r="P9" t="n">
-        <v>3.98</v>
+        <v>2.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.6</v>
+        <v>3.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>5.15</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>3.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1617,10 +1617,10 @@
         <v>4.5</v>
       </c>
       <c r="N10" t="n">
-        <v>11.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="P10" t="n">
         <v>2.25</v>
@@ -1653,19 +1653,19 @@
         <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
         <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>3.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
         <v>2.38</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="M11" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="O11" t="n">
         <v>3.5</v>
@@ -1745,7 +1745,7 @@
         <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.51</v>
@@ -1775,7 +1775,7 @@
         <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
         <v>1.56</v>
@@ -1855,7 +1855,7 @@
         <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
         <v>4.38</v>
@@ -1873,10 +1873,10 @@
         <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
         <v>9.199999999999999</v>
@@ -1888,22 +1888,22 @@
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC12" t="n">
         <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE12" t="n">
         <v>2.09</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>24</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>1.06</v>
       </c>
       <c r="O2" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>12</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -936,19 +936,19 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="AA4" t="n">
         <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AD4" t="n">
         <v>1.28</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>19</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>2.86</v>
       </c>
       <c r="P7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3.72</v>
       </c>
-      <c r="Q7" t="n">
-        <v>12.21</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.55</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.08</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>1.13</v>
       </c>
       <c r="M8" t="n">
-        <v>3.44</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>19</v>
       </c>
       <c r="O8" t="n">
-        <v>2.47</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>2.21</v>
+        <v>3.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.19</v>
+        <v>12.21</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>4.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.87</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>6.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>1.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>6.15</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.86</v>
+        <v>2.47</v>
       </c>
       <c r="P9" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.64</v>
+        <v>4.19</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.76</v>
       </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>2.98</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>9.199999999999999</v>
+        <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>1.82</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.57</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.38</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.05</v>
+        <v>1.31</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.98</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.41</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.51</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>3.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -136,6 +136,9 @@
     <t>16:30</t>
   </si>
   <si>
+    <t>17:30</t>
+  </si>
+  <si>
     <t>19:30</t>
   </si>
   <si>
@@ -154,6 +157,9 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Jamaica Jamaica National Premier League</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -166,33 +172,33 @@
     <t>2026</t>
   </si>
   <si>
+    <t>Sarıyer</t>
+  </si>
+  <si>
     <t>Adana Demirspor</t>
   </si>
   <si>
-    <t>Sarıyer</t>
-  </si>
-  <si>
     <t>Van BB</t>
   </si>
   <si>
     <t>Sakaryaspor</t>
   </si>
   <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>Al Salt</t>
+    <t>Al Kholood</t>
+  </si>
+  <si>
+    <t>Al Ittifaq</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Al Ittifaq</t>
-  </si>
-  <si>
-    <t>Al Kholood</t>
-  </si>
-  <si>
     <t>Pharco</t>
   </si>
   <si>
@@ -202,18 +208,21 @@
     <t>Al Ahly</t>
   </si>
   <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
     <t>Atlético PR</t>
   </si>
   <si>
     <t>Austria Klagenfurt</t>
   </si>
   <si>
+    <t>Amed</t>
+  </si>
+  <si>
     <t>Sivasspor</t>
   </si>
   <si>
-    <t>Amed</t>
-  </si>
-  <si>
     <t>BB Bodrumspor</t>
   </si>
   <si>
@@ -223,15 +232,15 @@
     <t>Al Jazeera</t>
   </si>
   <si>
+    <t>Al Riyadh</t>
+  </si>
+  <si>
+    <t>Al Fateh</t>
+  </si>
+  <si>
     <t>Al Najma</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
-    <t>Al Riyadh</t>
-  </si>
-  <si>
     <t>Petrojet</t>
   </si>
   <si>
@@ -241,6 +250,9 @@
     <t>El Gounah</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Corinthians</t>
   </si>
   <si>
@@ -248,6 +260,9 @@
   </si>
   <si>
     <t>incomplete</t>
+  </si>
+  <si>
+    <t>suspended</t>
   </si>
   <si>
     <t>canceled</t>
@@ -614,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -732,16 +747,16 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -756,76 +771,76 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L2">
-        <v>19.74</v>
+        <v>3.6</v>
       </c>
       <c r="M2">
-        <v>11.5</v>
+        <v>3.6</v>
       </c>
       <c r="N2">
-        <v>1.06</v>
+        <v>1.85</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3">
         <v>46072.3125</v>
@@ -839,16 +854,16 @@
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -863,76 +878,76 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L3">
-        <v>3.6</v>
+        <v>16.12</v>
       </c>
       <c r="M3">
-        <v>3.3</v>
+        <v>18</v>
       </c>
       <c r="N3">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="P3">
-        <v>2.25</v>
+        <v>3.88</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="R3">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="S3">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="T3">
-        <v>2.55</v>
+        <v>1.52</v>
       </c>
       <c r="U3">
-        <v>1.36</v>
+        <v>2.29</v>
       </c>
       <c r="V3">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3">
+        <v>1.02</v>
+      </c>
+      <c r="Z3">
+        <v>14.5</v>
+      </c>
+      <c r="AA3">
+        <v>1.08</v>
+      </c>
+      <c r="AB3">
+        <v>5.55</v>
+      </c>
+      <c r="AC3">
         <v>1.25</v>
       </c>
-      <c r="Z3">
-        <v>3.4</v>
-      </c>
-      <c r="AA3">
-        <v>1.81</v>
-      </c>
-      <c r="AB3">
-        <v>1.8</v>
-      </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>3.14</v>
       </c>
-      <c r="AD3">
-        <v>1.27</v>
-      </c>
       <c r="AE3">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="AF3">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>1.24</v>
+        <v>7.1</v>
       </c>
       <c r="AH3">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" s="3">
         <v>46072.3125</v>
@@ -946,16 +961,16 @@
         <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -970,22 +985,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O4">
         <v>2.96</v>
       </c>
       <c r="P4">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -997,7 +1012,7 @@
         <v>3.02</v>
       </c>
       <c r="T4">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="U4">
         <v>1.4</v>
@@ -1021,7 +1036,7 @@
         <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>2.97</v>
@@ -1033,7 +1048,7 @@
         <v>1.63</v>
       </c>
       <c r="AF4">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG4">
         <v>1.23</v>
@@ -1053,16 +1068,16 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1077,76 +1092,76 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L5">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="M5">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N5">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="O5">
-        <v>4.36</v>
+        <v>4.01</v>
       </c>
       <c r="P5">
         <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="R5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S5">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T5">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U5">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB5">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC5">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AD5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE5">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG5">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH5">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" s="3">
         <v>46072.58333333334</v>
@@ -1160,16 +1175,16 @@
         <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1184,76 +1199,76 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M6">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N6">
-        <v>6.9</v>
+        <v>4.13</v>
       </c>
       <c r="O6">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="P6">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q6">
-        <v>6.75</v>
+        <v>5.16</v>
       </c>
       <c r="R6">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="T6">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="U6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V6">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6">
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="Z6">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AA6">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AB6">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC6">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE6">
-        <v>2.46</v>
+        <v>2.11</v>
       </c>
       <c r="AF6">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH6">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="AI6" s="3">
         <v>46072.65625</v>
@@ -1267,16 +1282,16 @@
         <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1291,76 +1306,76 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L7">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N7">
-        <v>3.95</v>
+        <v>6.77</v>
       </c>
       <c r="O7">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="P7">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="Q7">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="R7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="T7">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V7">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W7">
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="AA7">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AB7">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>4.45</v>
+        <v>3.96</v>
       </c>
       <c r="AD7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE7">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AF7">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AG7">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AH7">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="AI7" s="3">
         <v>46072.65625</v>
@@ -1374,16 +1389,16 @@
         <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1398,76 +1413,76 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L8">
+        <v>2.05</v>
+      </c>
+      <c r="M8">
+        <v>3.4</v>
+      </c>
+      <c r="N8">
+        <v>3.6</v>
+      </c>
+      <c r="O8">
+        <v>2.55</v>
+      </c>
+      <c r="P8">
+        <v>2.2</v>
+      </c>
+      <c r="Q8">
+        <v>4.2</v>
+      </c>
+      <c r="R8">
+        <v>1.36</v>
+      </c>
+      <c r="S8">
+        <v>2.9</v>
+      </c>
+      <c r="T8">
+        <v>2.78</v>
+      </c>
+      <c r="U8">
+        <v>1.38</v>
+      </c>
+      <c r="V8">
+        <v>6.65</v>
+      </c>
+      <c r="W8">
         <v>1.08</v>
       </c>
-      <c r="M8">
-        <v>11.81</v>
-      </c>
-      <c r="N8">
-        <v>16.08</v>
-      </c>
-      <c r="O8">
-        <v>1.34</v>
-      </c>
-      <c r="P8">
-        <v>3.72</v>
-      </c>
-      <c r="Q8">
-        <v>8</v>
-      </c>
-      <c r="R8">
-        <v>1.14</v>
-      </c>
-      <c r="S8">
-        <v>4.5</v>
-      </c>
-      <c r="T8">
-        <v>1.86</v>
-      </c>
-      <c r="U8">
-        <v>1.83</v>
-      </c>
-      <c r="V8">
-        <v>3.58</v>
-      </c>
-      <c r="W8">
-        <v>1.21</v>
-      </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>6.6</v>
+        <v>3.41</v>
       </c>
       <c r="AA8">
-        <v>1.28</v>
+        <v>1.98</v>
       </c>
       <c r="AB8">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="AC8">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AF8">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AG8">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AH8">
-        <v>6.15</v>
+        <v>1.69</v>
       </c>
       <c r="AI8" s="3">
         <v>46072.66666666666</v>
@@ -1481,16 +1496,16 @@
         <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1505,73 +1520,73 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L9">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="M9">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N9">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="O9">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="P9">
         <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U9">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V9">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AA9">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD9">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF9">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AG9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH9">
         <v>1.53</v>
@@ -1588,16 +1603,16 @@
         <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1612,76 +1627,76 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L10">
+        <v>1.07</v>
+      </c>
+      <c r="M10">
+        <v>12</v>
+      </c>
+      <c r="N10">
+        <v>17</v>
+      </c>
+      <c r="O10">
+        <v>1.34</v>
+      </c>
+      <c r="P10">
+        <v>3.7</v>
+      </c>
+      <c r="Q10">
+        <v>11.2</v>
+      </c>
+      <c r="R10">
+        <v>1.11</v>
+      </c>
+      <c r="S10">
+        <v>4.5</v>
+      </c>
+      <c r="T10">
         <v>1.93</v>
       </c>
-      <c r="M10">
-        <v>3.44</v>
-      </c>
-      <c r="N10">
-        <v>3.38</v>
-      </c>
-      <c r="O10">
-        <v>2.5</v>
-      </c>
-      <c r="P10">
-        <v>2.05</v>
-      </c>
-      <c r="Q10">
-        <v>3.64</v>
-      </c>
-      <c r="R10">
-        <v>1.36</v>
-      </c>
-      <c r="S10">
-        <v>2.82</v>
-      </c>
-      <c r="T10">
-        <v>2.78</v>
-      </c>
       <c r="U10">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="V10">
-        <v>6.6</v>
+        <v>3.58</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>3.14</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="AC10">
-        <v>3.33</v>
+        <v>1.86</v>
       </c>
       <c r="AD10">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AE10">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="AF10">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AG10">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AH10">
-        <v>1.7</v>
+        <v>6.15</v>
       </c>
       <c r="AI10" s="3">
         <v>46072.66666666666</v>
@@ -1695,16 +1710,16 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1719,37 +1734,37 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L11">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="M11">
         <v>2.74</v>
       </c>
       <c r="N11">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="O11">
         <v>3.9</v>
       </c>
       <c r="P11">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="Q11">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S11">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="T11">
         <v>3.5</v>
       </c>
       <c r="U11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V11">
         <v>9.1</v>
@@ -1764,13 +1779,13 @@
         <v>1.51</v>
       </c>
       <c r="Z11">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AA11">
         <v>2.5</v>
       </c>
       <c r="AB11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC11">
         <v>4.7</v>
@@ -1779,7 +1794,7 @@
         <v>1.12</v>
       </c>
       <c r="AE11">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF11">
         <v>1.65</v>
@@ -1788,7 +1803,7 @@
         <v>1.35</v>
       </c>
       <c r="AH11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3">
         <v>46072.6875</v>
@@ -1802,16 +1817,16 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1826,25 +1841,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L12">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="M12">
         <v>2.87</v>
       </c>
       <c r="N12">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
         <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R12">
         <v>1.51</v>
@@ -1853,7 +1868,7 @@
         <v>2.31</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U12">
         <v>1.3</v>
@@ -1862,7 +1877,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
         <v>1.05</v>
@@ -1874,10 +1889,10 @@
         <v>2.62</v>
       </c>
       <c r="AA12">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB12">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC12">
         <v>4</v>
@@ -1892,7 +1907,7 @@
         <v>1.78</v>
       </c>
       <c r="AG12">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH12">
         <v>1.3</v>
@@ -1909,16 +1924,16 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1933,40 +1948,40 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="N13">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O13">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P13">
         <v>2.25</v>
       </c>
       <c r="Q13">
-        <v>9.5</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="R13">
         <v>1.38</v>
       </c>
       <c r="S13">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T13">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U13">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V13">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W13">
         <v>1.05</v>
@@ -1975,19 +1990,19 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
         <v>3.2</v>
       </c>
       <c r="AA13">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB13">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC13">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
         <v>1.28</v>
@@ -1999,10 +2014,10 @@
         <v>1.51</v>
       </c>
       <c r="AG13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AH13">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AI13" s="3">
         <v>46072.6875</v>
@@ -2016,16 +2031,16 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2040,79 +2055,79 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L14">
-        <v>2.45</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="N14">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="Q14">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="R14">
+        <v>1.33</v>
+      </c>
+      <c r="S14">
+        <v>2.88</v>
+      </c>
+      <c r="T14">
+        <v>2.53</v>
+      </c>
+      <c r="U14">
+        <v>1.42</v>
+      </c>
+      <c r="V14">
+        <v>6</v>
+      </c>
+      <c r="W14">
+        <v>1.1</v>
+      </c>
+      <c r="X14">
+        <v>1.01</v>
+      </c>
+      <c r="Y14">
+        <v>1.21</v>
+      </c>
+      <c r="Z14">
+        <v>3.58</v>
+      </c>
+      <c r="AA14">
+        <v>1.73</v>
+      </c>
+      <c r="AB14">
+        <v>2.01</v>
+      </c>
+      <c r="AC14">
+        <v>2.7</v>
+      </c>
+      <c r="AD14">
+        <v>1.36</v>
+      </c>
+      <c r="AE14">
+        <v>2.16</v>
+      </c>
+      <c r="AF14">
         <v>1.59</v>
       </c>
-      <c r="S14">
-        <v>2.48</v>
-      </c>
-      <c r="T14">
-        <v>3.45</v>
-      </c>
-      <c r="U14">
-        <v>1.29</v>
-      </c>
-      <c r="V14">
-        <v>8</v>
-      </c>
-      <c r="W14">
+      <c r="AG14">
+        <v>3.14</v>
+      </c>
+      <c r="AH14">
         <v>1.05</v>
       </c>
-      <c r="X14">
-        <v>1.07</v>
-      </c>
-      <c r="Y14">
-        <v>1.42</v>
-      </c>
-      <c r="Z14">
-        <v>2.63</v>
-      </c>
-      <c r="AA14">
-        <v>2.35</v>
-      </c>
-      <c r="AB14">
-        <v>1.57</v>
-      </c>
-      <c r="AC14">
-        <v>4.33</v>
-      </c>
-      <c r="AD14">
-        <v>1.17</v>
-      </c>
-      <c r="AE14">
-        <v>1.91</v>
-      </c>
-      <c r="AF14">
-        <v>1.8</v>
-      </c>
-      <c r="AG14">
-        <v>1.37</v>
-      </c>
-      <c r="AH14">
-        <v>1.45</v>
-      </c>
       <c r="AI14" s="3">
-        <v>46072.8125</v>
+        <v>46072.72916666666</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2123,16 +2138,16 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2147,78 +2162,185 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3">
+        <v>46072.8125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35">
+      <c r="A16" s="2">
+        <v>46072</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3">
         <v>46072.875</v>
       </c>
     </row>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,16 +633,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.2</v>
+        <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>2.81</v>
+        <v>19.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>1.27</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>7.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>6.45</v>
+        <v>2.59</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.74</v>
+        <v>14.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.74</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.99</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.83</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>2.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>30</v>
+        <v>3.49</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>7.3</v>
+        <v>2.77</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>2.59</v>
+        <v>6.65</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.97</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46072.3125</v>
@@ -871,16 +871,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.49</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.2</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46072.3125</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1135,37 +1135,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.83</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1174,34 +1174,34 @@
         <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
         <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46072.65625</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="O7" t="n">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.65625</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.07</v>
+        <v>2.33</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>17</v>
+        <v>2.53</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.2</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
-        <v>3.58</v>
+        <v>6.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.11</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.15</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -1516,16 +1516,16 @@
         <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1534,31 +1534,31 @@
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>17</v>
       </c>
       <c r="O10" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>2.96</v>
+        <v>4.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.86</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="AE10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF10" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>6.15</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
-        <v>9.4</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.12</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1852,70 +1852,70 @@
         <v>3.12</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="N12" t="n">
         <v>2.35</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.87</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="N13" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2.4</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46072.6875</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
         <v>1.33</v>
       </c>
       <c r="O14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
@@ -2132,28 +2132,28 @@
         <v>3.58</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
         <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46072.72916666666</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -1109,87 +1109,87 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>5.25</v>
+        <v>4.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>2.1</v>
@@ -1201,7 +1201,7 @@
         <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46072.65625</v>
@@ -1228,19 +1228,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1250,65 +1250,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="N7" t="n">
-        <v>4.55</v>
+        <v>5.25</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
         <v>2.1</v>
@@ -1320,7 +1320,7 @@
         <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.65625</v>
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2.53</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.25</v>
       </c>
       <c r="AG8" t="n">
         <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>7.5</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>3.78</v>
       </c>
       <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V9" t="n">
         <v>3.8</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>6.15</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.07</v>
+        <v>2.33</v>
       </c>
       <c r="M10" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>17</v>
+        <v>2.53</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.78</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3.8</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.25</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.15</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1704,29 +1704,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1736,67 +1736,67 @@
         <v>2.87</v>
       </c>
       <c r="N11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.3</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1823,19 +1823,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1845,77 +1845,77 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
         <v>3.12</v>
       </c>
       <c r="M12" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.5</v>
       </c>
-      <c r="S12" t="n">
+      <c r="Z12" t="n">
         <v>2.4</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
         <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46072.6875</v>
@@ -1951,75 +1951,75 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>4.33</v>
+        <v>4.63</v>
       </c>
       <c r="N13" t="n">
         <v>9.18</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>7.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
         <v>1.29</v>
@@ -2034,7 +2034,7 @@
         <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46072.6875</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>4.23</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
         <v>8.449999999999999</v>

--- a/jogos_2026-02-19.xlsx
+++ b/jogos_2026-02-19.xlsx
@@ -633,16 +633,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>30</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="O2" t="n">
-        <v>19.5</v>
+        <v>2.81</v>
       </c>
       <c r="P2" t="n">
-        <v>4.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.27</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>7.3</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>2.59</v>
+        <v>6.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>1.99</v>
       </c>
       <c r="AC2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46072.3125</v>
@@ -871,16 +871,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>30</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>2.81</v>
+        <v>19.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>1.27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>7.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>6.45</v>
+        <v>2.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.74</v>
+        <v>14.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.99</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.83</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>2.97</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46072.3125</v>
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,61 +1135,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="N6" t="n">
-        <v>4.55</v>
+        <v>5.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
         <v>2.1</v>
@@ -1201,7 +1201,7 @@
         <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46072.65625</v>
@@ -1228,25 +1228,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1254,61 +1254,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>5.25</v>
+        <v>4.55</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
         <v>2.1</v>
@@ -1320,7 +1320,7 @@
         <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46072.65625</v>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>7.5</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>17</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>3.78</v>
       </c>
       <c r="Q8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V8" t="n">
         <v>3.8</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>6.15</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1466,25 +1466,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>7.5</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>3.78</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.91</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3</v>
-      </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.15</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46072.66666666666</v>
@@ -1704,19 +1704,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="AA11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46072.6875</v>
@@ -1942,19 +1942,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>4.63</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>9.18</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="P13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q13" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.2</v>
+        <v>1.38</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46072.6875</v>
@@ -2070,20 +2070,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
